--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.330389881033538</v>
+        <v>1.19118835566795</v>
       </c>
       <c r="D2" t="n">
-        <v>7.321321237656803</v>
+        <v>1.189714701119231</v>
       </c>
       <c r="E2" t="n">
-        <v>22.6930426981351</v>
+        <v>3.687619438446954</v>
       </c>
       <c r="F2" t="n">
-        <v>22.57468336387036</v>
+        <v>3.668386046628934</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.06085590521097</v>
+        <v>6.997389084596783</v>
       </c>
       <c r="D3" t="n">
-        <v>43.02692276810536</v>
+        <v>6.991874949817121</v>
       </c>
       <c r="E3" t="n">
-        <v>22.6930426981351</v>
+        <v>3.687619438446954</v>
       </c>
       <c r="F3" t="n">
-        <v>22.57468336387036</v>
+        <v>3.668386046628934</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>62.07223050985605</v>
+        <v>10.08673745785161</v>
       </c>
       <c r="D4" t="n">
-        <v>61.74058197533598</v>
+        <v>10.0328445709921</v>
       </c>
       <c r="E4" t="n">
-        <v>22.6930426981351</v>
+        <v>3.687619438446954</v>
       </c>
       <c r="F4" t="n">
-        <v>22.57468336387036</v>
+        <v>3.668386046628934</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
